--- a/output/ap_prepayment_opening_db/未匹配清单_预付期初_20260616.xlsx
+++ b/output/ap_prepayment_opening_db/未匹配清单_预付期初_20260616.xlsx
@@ -1888,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2752</v>
+        <v>8430</v>
       </c>
       <c r="D2" t="n">
-        <v>2752</v>
+        <v>8430</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1944,28 +1944,6 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>费用项目编码</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2752</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2752</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
